--- a/snapshots/mkt_snapshot.xlsx
+++ b/snapshots/mkt_snapshot.xlsx
@@ -2276,12 +2276,24 @@
       <c r="J22" t="n">
         <v>126866.73</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>180</v>
+      </c>
+      <c r="L22" t="n">
+        <v>241684</v>
+      </c>
+      <c r="M22" t="n">
+        <v>185709</v>
+      </c>
+      <c r="N22" t="n">
+        <v>205</v>
+      </c>
+      <c r="O22" t="n">
+        <v>245499</v>
+      </c>
+      <c r="P22" t="n">
+        <v>282791</v>
+      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
@@ -2341,12 +2353,24 @@
       <c r="J23" t="n">
         <v>125305.89</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>227</v>
+      </c>
+      <c r="L23" t="n">
+        <v>301973</v>
+      </c>
+      <c r="M23" t="n">
+        <v>156406</v>
+      </c>
+      <c r="N23" t="n">
+        <v>248</v>
+      </c>
+      <c r="O23" t="n">
+        <v>280214</v>
+      </c>
+      <c r="P23" t="n">
+        <v>333204</v>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -2406,12 +2430,24 @@
       <c r="J24" t="n">
         <v>75734.33</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>179</v>
+      </c>
+      <c r="L24" t="n">
+        <v>211755</v>
+      </c>
+      <c r="M24" t="n">
+        <v>148967</v>
+      </c>
+      <c r="N24" t="n">
+        <v>263</v>
+      </c>
+      <c r="O24" t="n">
+        <v>290691</v>
+      </c>
+      <c r="P24" t="n">
+        <v>276298</v>
+      </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
@@ -2471,12 +2507,24 @@
       <c r="J25" t="n">
         <v>108754.3</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>179</v>
+      </c>
+      <c r="L25" t="n">
+        <v>230832</v>
+      </c>
+      <c r="M25" t="n">
+        <v>172007</v>
+      </c>
+      <c r="N25" t="n">
+        <v>286</v>
+      </c>
+      <c r="O25" t="n">
+        <v>293352</v>
+      </c>
+      <c r="P25" t="n">
+        <v>323498</v>
+      </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
@@ -2536,12 +2584,24 @@
       <c r="J26" t="n">
         <v>32875.25</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>132</v>
+      </c>
+      <c r="L26" t="n">
+        <v>167691</v>
+      </c>
+      <c r="M26" t="n">
+        <v>171436</v>
+      </c>
+      <c r="N26" t="n">
+        <v>247</v>
+      </c>
+      <c r="O26" t="n">
+        <v>273597</v>
+      </c>
+      <c r="P26" t="n">
+        <v>331583</v>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
@@ -2601,12 +2661,24 @@
       <c r="J27" t="n">
         <v>70850.44</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>133</v>
+      </c>
+      <c r="L27" t="n">
+        <v>176129</v>
+      </c>
+      <c r="M27" t="n">
+        <v>129972</v>
+      </c>
+      <c r="N27" t="n">
+        <v>339</v>
+      </c>
+      <c r="O27" t="n">
+        <v>369336</v>
+      </c>
+      <c r="P27" t="n">
+        <v>354744</v>
+      </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
@@ -2654,16 +2726,36 @@
       <c r="F28" t="n">
         <v>127998</v>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>533</v>
+      </c>
+      <c r="H28" t="n">
+        <v>613669</v>
+      </c>
+      <c r="I28" t="n">
+        <v>433966</v>
+      </c>
+      <c r="J28" t="n">
+        <v>121805.71</v>
+      </c>
+      <c r="K28" t="n">
+        <v>130</v>
+      </c>
+      <c r="L28" t="n">
+        <v>166479</v>
+      </c>
+      <c r="M28" t="n">
+        <v>123303</v>
+      </c>
+      <c r="N28" t="n">
+        <v>398</v>
+      </c>
+      <c r="O28" t="n">
+        <v>438337</v>
+      </c>
+      <c r="P28" t="n">
+        <v>283140</v>
+      </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
@@ -2677,24 +2769,34 @@
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>88</v>
+        <v>621</v>
       </c>
       <c r="AD28" t="n">
-        <v>133334</v>
+        <v>747003</v>
       </c>
       <c r="AE28" t="n">
-        <v>70556</v>
+        <v>504522</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
         <v>46230</v>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>53</v>
+      </c>
+      <c r="C29" t="n">
+        <v>73912</v>
+      </c>
+      <c r="D29" t="n">
+        <v>153078</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>70837</v>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2718,13 +2820,13 @@
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>73912</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>153078</v>
       </c>
     </row>
     <row r="30">
@@ -2933,49 +3035,49 @@
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1989</v>
+        <v>2042</v>
       </c>
       <c r="C35" t="n">
-        <v>2650381</v>
+        <v>2724293</v>
       </c>
       <c r="D35" t="n">
-        <v>1855075</v>
+        <v>2008153</v>
       </c>
       <c r="E35" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F35" t="n">
-        <v>2290173</v>
+        <v>2361010</v>
       </c>
       <c r="G35" t="n">
-        <v>12478</v>
+        <v>13011</v>
       </c>
       <c r="H35" t="n">
-        <v>14398882</v>
+        <v>15012551</v>
       </c>
       <c r="I35" t="n">
-        <v>11744027.76</v>
+        <v>12177993.76</v>
       </c>
       <c r="J35" t="n">
-        <v>3310625.48</v>
+        <v>3432431.19</v>
       </c>
       <c r="K35" t="n">
-        <v>3759</v>
+        <v>4919</v>
       </c>
       <c r="L35" t="n">
-        <v>4549118</v>
+        <v>6045661</v>
       </c>
       <c r="M35" t="n">
-        <v>2965965</v>
+        <v>4053765</v>
       </c>
       <c r="N35" t="n">
-        <v>5989</v>
+        <v>7975</v>
       </c>
       <c r="O35" t="n">
-        <v>6572344</v>
+        <v>8763370</v>
       </c>
       <c r="P35" t="n">
-        <v>5869869</v>
+        <v>8055127</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3014,38 +3116,38 @@
         <v>2057025</v>
       </c>
       <c r="AC35" t="n">
-        <v>24454</v>
+        <v>25040</v>
       </c>
       <c r="AD35" t="n">
-        <v>25069153</v>
+        <v>25756734</v>
       </c>
       <c r="AE35" t="n">
-        <v>17524040.18855</v>
+        <v>18111084.18855</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.4287190544856677</v>
+        <v>0.3566162538412163</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0.2260599424877381</v>
+        <v>0.2327606086735259</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>0.5337733250392368</v>
+        <v>0.4913693813035536</v>
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>0.1196747320936805</v>
+        <v>0.08792449827296329</v>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
@@ -3066,21 +3168,21 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="n">
-        <v>0.4305578354231289</v>
+        <v>0.4221530711167286</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>3912467.190476191</v>
+        <v>3248195.5</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>17854613.68</v>
+        <v>17899580.03846154</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -3095,7 +3197,7 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
-        <v>96309.25</v>
+        <v>46228.44</v>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
@@ -3105,12 +3207,12 @@
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="n">
-        <v>12849210.66666667</v>
+        <v>8566140.444444444</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="n">
-        <v>39621566.62924813</v>
+        <v>34669110.26501124</v>
       </c>
     </row>
     <row r="39">
@@ -3178,7 +3280,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="n">
-        <v>97778100.77924812</v>
+        <v>92825644.41501124</v>
       </c>
     </row>
     <row r="41">

--- a/snapshots/mkt_snapshot.xlsx
+++ b/snapshots/mkt_snapshot.xlsx
@@ -719,19 +719,19 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="AA3" t="n">
-        <v>189946</v>
+        <v>200446</v>
       </c>
       <c r="AB3" t="n">
         <v>172188</v>
       </c>
       <c r="AC3" t="n">
-        <v>794</v>
+        <v>829</v>
       </c>
       <c r="AD3" t="n">
-        <v>894032</v>
+        <v>904532</v>
       </c>
       <c r="AE3" t="n">
         <v>726084</v>
@@ -802,19 +802,19 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="AA4" t="n">
-        <v>155426</v>
+        <v>164726</v>
       </c>
       <c r="AB4" t="n">
         <v>171334</v>
       </c>
       <c r="AC4" t="n">
-        <v>733</v>
+        <v>764</v>
       </c>
       <c r="AD4" t="n">
-        <v>842852</v>
+        <v>852152</v>
       </c>
       <c r="AE4" t="n">
         <v>716419</v>
@@ -885,19 +885,19 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>336</v>
+        <v>485</v>
       </c>
       <c r="AA5" t="n">
-        <v>356177</v>
+        <v>400877</v>
       </c>
       <c r="AB5" t="n">
         <v>120659</v>
       </c>
       <c r="AC5" t="n">
-        <v>811</v>
+        <v>960</v>
       </c>
       <c r="AD5" t="n">
-        <v>947187</v>
+        <v>991887</v>
       </c>
       <c r="AE5" t="n">
         <v>633156</v>
@@ -968,19 +968,19 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>475</v>
+        <v>654</v>
       </c>
       <c r="AA6" t="n">
-        <v>499937</v>
+        <v>553605</v>
       </c>
       <c r="AB6" t="n">
         <v>93565</v>
       </c>
       <c r="AC6" t="n">
-        <v>2634</v>
+        <v>2813</v>
       </c>
       <c r="AD6" t="n">
-        <v>2906066</v>
+        <v>2959734</v>
       </c>
       <c r="AE6" t="n">
         <v>583575</v>
@@ -1055,19 +1055,19 @@
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>378</v>
+        <v>516</v>
       </c>
       <c r="AA7" t="n">
-        <v>401844</v>
+        <v>443244</v>
       </c>
       <c r="AB7" t="n">
         <v>88972</v>
       </c>
       <c r="AC7" t="n">
-        <v>3145</v>
+        <v>3283</v>
       </c>
       <c r="AD7" t="n">
-        <v>2733425</v>
+        <v>2774825</v>
       </c>
       <c r="AE7" t="n">
         <v>620331</v>
@@ -1138,19 +1138,19 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>264</v>
+        <v>335</v>
       </c>
       <c r="AA8" t="n">
-        <v>272947</v>
+        <v>294197</v>
       </c>
       <c r="AB8" t="n">
         <v>221739</v>
       </c>
       <c r="AC8" t="n">
-        <v>1044</v>
+        <v>1115</v>
       </c>
       <c r="AD8" t="n">
-        <v>1155547</v>
+        <v>1176797</v>
       </c>
       <c r="AE8" t="n">
         <v>779394</v>
@@ -1223,19 +1223,19 @@
         <v>778209</v>
       </c>
       <c r="Z9" t="n">
-        <v>356</v>
+        <v>422</v>
       </c>
       <c r="AA9" t="n">
-        <v>364129</v>
+        <v>383929</v>
       </c>
       <c r="AB9" t="n">
         <v>168924</v>
       </c>
       <c r="AC9" t="n">
-        <v>784</v>
+        <v>850</v>
       </c>
       <c r="AD9" t="n">
-        <v>857388</v>
+        <v>877188</v>
       </c>
       <c r="AE9" t="n">
         <v>1525107</v>
@@ -1306,19 +1306,19 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>254</v>
+        <v>347</v>
       </c>
       <c r="AA10" t="n">
-        <v>261985</v>
+        <v>289885</v>
       </c>
       <c r="AB10" t="n">
         <v>86788</v>
       </c>
       <c r="AC10" t="n">
-        <v>658</v>
+        <v>751</v>
       </c>
       <c r="AD10" t="n">
-        <v>769873</v>
+        <v>797773</v>
       </c>
       <c r="AE10" t="n">
         <v>553085</v>
@@ -1389,19 +1389,19 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>212</v>
+        <v>313</v>
       </c>
       <c r="AA11" t="n">
-        <v>229359</v>
+        <v>259659</v>
       </c>
       <c r="AB11" t="n">
         <v>87491</v>
       </c>
       <c r="AC11" t="n">
-        <v>634</v>
+        <v>735</v>
       </c>
       <c r="AD11" t="n">
-        <v>726995</v>
+        <v>757295</v>
       </c>
       <c r="AE11" t="n">
         <v>662792</v>
@@ -1472,19 +1472,19 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>170</v>
+        <v>243</v>
       </c>
       <c r="AA12" t="n">
-        <v>191347</v>
+        <v>213247</v>
       </c>
       <c r="AB12" t="n">
         <v>110027</v>
       </c>
       <c r="AC12" t="n">
-        <v>585</v>
+        <v>658</v>
       </c>
       <c r="AD12" t="n">
-        <v>692818</v>
+        <v>714718</v>
       </c>
       <c r="AE12" t="n">
         <v>647206</v>
@@ -1555,19 +1555,19 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>382</v>
+        <v>556</v>
       </c>
       <c r="AA13" t="n">
-        <v>408833</v>
+        <v>461033</v>
       </c>
       <c r="AB13" t="n">
         <v>104409</v>
       </c>
       <c r="AC13" t="n">
-        <v>981</v>
+        <v>1155</v>
       </c>
       <c r="AD13" t="n">
-        <v>1122908</v>
+        <v>1175108</v>
       </c>
       <c r="AE13" t="n">
         <v>585582</v>
@@ -1642,19 +1642,19 @@
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>312</v>
+        <v>470</v>
       </c>
       <c r="AA14" t="n">
-        <v>343453</v>
+        <v>390853</v>
       </c>
       <c r="AB14" t="n">
         <v>151404</v>
       </c>
       <c r="AC14" t="n">
-        <v>3090</v>
+        <v>3248</v>
       </c>
       <c r="AD14" t="n">
-        <v>2204637</v>
+        <v>2252037</v>
       </c>
       <c r="AE14" t="n">
         <v>669455</v>
@@ -1725,19 +1725,19 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="n">
-        <v>151740</v>
+        <v>169440</v>
       </c>
       <c r="AB15" t="n">
         <v>194876</v>
       </c>
       <c r="AC15" t="n">
-        <v>528</v>
+        <v>587</v>
       </c>
       <c r="AD15" t="n">
-        <v>622473</v>
+        <v>640173</v>
       </c>
       <c r="AE15" t="n">
         <v>690362</v>
@@ -1810,19 +1810,19 @@
         <v>613268</v>
       </c>
       <c r="Z16" t="n">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="AA16" t="n">
-        <v>175258</v>
+        <v>189358</v>
       </c>
       <c r="AB16" t="n">
         <v>180051</v>
       </c>
       <c r="AC16" t="n">
-        <v>559</v>
+        <v>583</v>
       </c>
       <c r="AD16" t="n">
-        <v>632904</v>
+        <v>647004</v>
       </c>
       <c r="AE16" t="n">
         <v>1385509</v>
@@ -1891,26 +1891,24 @@
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="n">
-        <v>87050.28571</v>
-      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="AA17" t="n">
-        <v>175516</v>
+        <v>191616</v>
       </c>
       <c r="AB17" t="n">
         <v>104598</v>
       </c>
       <c r="AC17" t="n">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="AD17" t="n">
-        <v>598170</v>
+        <v>614270</v>
       </c>
       <c r="AE17" t="n">
-        <v>697537.28571</v>
+        <v>610487</v>
       </c>
     </row>
     <row r="18">
@@ -1976,24 +1974,24 @@
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="n">
-        <v>87050.28571</v>
-      </c>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="AA18" t="n">
-        <v>139526</v>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+        <v>163403</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>125511</v>
+      </c>
       <c r="AC18" t="n">
-        <v>551</v>
+        <v>592</v>
       </c>
       <c r="AD18" t="n">
-        <v>616586</v>
+        <v>640463</v>
       </c>
       <c r="AE18" t="n">
-        <v>648415.28571</v>
+        <v>686876</v>
       </c>
     </row>
     <row r="19">
@@ -2059,24 +2057,24 @@
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="n">
-        <v>87050.28571</v>
-      </c>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>364</v>
+        <v>166</v>
       </c>
       <c r="AA19" t="n">
-        <v>336241</v>
-      </c>
-      <c r="AB19" t="inlineStr"/>
+        <v>142420</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>139950</v>
+      </c>
       <c r="AC19" t="n">
-        <v>761</v>
+        <v>563</v>
       </c>
       <c r="AD19" t="n">
-        <v>798642</v>
+        <v>604821</v>
       </c>
       <c r="AE19" t="n">
-        <v>729165.28571</v>
+        <v>782065</v>
       </c>
     </row>
     <row r="20">
@@ -2142,24 +2140,24 @@
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="n">
-        <v>87050.28571</v>
-      </c>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>360</v>
+        <v>391</v>
       </c>
       <c r="AA20" t="n">
-        <v>320224</v>
-      </c>
-      <c r="AB20" t="inlineStr"/>
+        <v>344341</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>100984</v>
+      </c>
       <c r="AC20" t="n">
-        <v>776</v>
+        <v>807</v>
       </c>
       <c r="AD20" t="n">
-        <v>820565</v>
+        <v>844682</v>
       </c>
       <c r="AE20" t="n">
-        <v>731221.28571</v>
+        <v>745155</v>
       </c>
     </row>
     <row r="21">
@@ -2229,20 +2227,24 @@
       <c r="X21" t="n">
         <v>970942</v>
       </c>
-      <c r="Y21" t="n">
-        <v>87050.28571</v>
-      </c>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>389</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>328924</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>122410</v>
+      </c>
       <c r="AC21" t="n">
-        <v>1999</v>
+        <v>2388</v>
       </c>
       <c r="AD21" t="n">
-        <v>1590969</v>
+        <v>1919893</v>
       </c>
       <c r="AE21" t="n">
-        <v>572537.28571</v>
+        <v>607897</v>
       </c>
     </row>
     <row r="22">
@@ -2309,17 +2311,23 @@
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>172</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>130392</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>191253</v>
+      </c>
       <c r="AC22" t="n">
-        <v>429</v>
+        <v>601</v>
       </c>
       <c r="AD22" t="n">
-        <v>604873</v>
+        <v>735265</v>
       </c>
       <c r="AE22" t="n">
-        <v>531320</v>
+        <v>722573</v>
       </c>
     </row>
     <row r="23">
@@ -2385,18 +2393,26 @@
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>609352</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>137</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>112685</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>174970</v>
+      </c>
       <c r="AC23" t="n">
-        <v>456</v>
+        <v>593</v>
       </c>
       <c r="AD23" t="n">
-        <v>573907</v>
+        <v>686592</v>
       </c>
       <c r="AE23" t="n">
-        <v>540539</v>
+        <v>1324861</v>
       </c>
     </row>
     <row r="24">
@@ -2462,18 +2478,26 @@
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>151</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>131461</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>141505</v>
+      </c>
       <c r="AC24" t="n">
-        <v>452</v>
+        <v>603</v>
       </c>
       <c r="AD24" t="n">
-        <v>515586</v>
+        <v>647047</v>
       </c>
       <c r="AE24" t="n">
-        <v>507047</v>
+        <v>752310</v>
       </c>
     </row>
     <row r="25">
@@ -2539,18 +2563,26 @@
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>202</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>190620</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>123916</v>
+      </c>
       <c r="AC25" t="n">
-        <v>499</v>
+        <v>701</v>
       </c>
       <c r="AD25" t="n">
-        <v>604299</v>
+        <v>794919</v>
       </c>
       <c r="AE25" t="n">
-        <v>580219.76</v>
+        <v>807893.76</v>
       </c>
     </row>
     <row r="26">
@@ -2616,18 +2648,26 @@
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>186</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>174329</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>119763</v>
+      </c>
       <c r="AC26" t="n">
-        <v>423</v>
+        <v>609</v>
       </c>
       <c r="AD26" t="n">
-        <v>496612</v>
+        <v>670941</v>
       </c>
       <c r="AE26" t="n">
-        <v>583273</v>
+        <v>806794</v>
       </c>
     </row>
     <row r="27">
@@ -2693,18 +2733,26 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>350</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>333052</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>241915</v>
+      </c>
       <c r="AC27" t="n">
-        <v>524</v>
+        <v>874</v>
       </c>
       <c r="AD27" t="n">
-        <v>606505</v>
+        <v>939557</v>
       </c>
       <c r="AE27" t="n">
-        <v>554152</v>
+        <v>899825</v>
       </c>
     </row>
     <row r="28">
@@ -2759,23 +2807,37 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>3314</v>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>312</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>291210</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>194522</v>
+      </c>
       <c r="AC28" t="n">
-        <v>621</v>
+        <v>933</v>
       </c>
       <c r="AD28" t="n">
-        <v>747003</v>
+        <v>1038213</v>
       </c>
       <c r="AE28" t="n">
-        <v>504522</v>
+        <v>806116</v>
       </c>
     </row>
     <row r="29">
@@ -2797,10 +2859,18 @@
       <c r="F29" t="n">
         <v>70837</v>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>397</v>
+      </c>
+      <c r="H29" t="n">
+        <v>453996</v>
+      </c>
+      <c r="I29" t="n">
+        <v>434403</v>
+      </c>
+      <c r="J29" t="n">
+        <v>38029</v>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -2813,35 +2883,65 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>1864</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1313698</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>193</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>172579</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>297136</v>
+      </c>
       <c r="AC29" t="n">
-        <v>53</v>
+        <v>2507</v>
       </c>
       <c r="AD29" t="n">
-        <v>73912</v>
+        <v>2014185</v>
       </c>
       <c r="AE29" t="n">
-        <v>153078</v>
+        <v>988375</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
         <v>46231</v>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>66</v>
+      </c>
+      <c r="C30" t="n">
+        <v>85641</v>
+      </c>
+      <c r="D30" t="n">
+        <v>60533</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>59797</v>
+      </c>
+      <c r="G30" t="n">
+        <v>395</v>
+      </c>
+      <c r="H30" t="n">
+        <v>431351</v>
+      </c>
+      <c r="I30" t="n">
+        <v>517181</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -2861,28 +2961,46 @@
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>516992</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>577714</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
         <v>46232</v>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>63</v>
+      </c>
+      <c r="C31" t="n">
+        <v>106264</v>
+      </c>
+      <c r="D31" t="n">
+        <v>89783</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" t="n">
+        <v>101469</v>
+      </c>
+      <c r="G31" t="n">
+        <v>413</v>
+      </c>
+      <c r="H31" t="n">
+        <v>458901</v>
+      </c>
+      <c r="I31" t="n">
+        <v>458013</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -2902,24 +3020,34 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>565165</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>547796</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
         <v>46233</v>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>54</v>
+      </c>
+      <c r="C32" t="n">
+        <v>93127</v>
+      </c>
+      <c r="D32" t="n">
+        <v>89783</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>86522</v>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2943,13 +3071,13 @@
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>93127</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>89783</v>
       </c>
     </row>
     <row r="33">
@@ -3035,31 +3163,31 @@
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>2042</v>
+        <v>2225</v>
       </c>
       <c r="C35" t="n">
-        <v>2724293</v>
+        <v>3009325</v>
       </c>
       <c r="D35" t="n">
-        <v>2008153</v>
+        <v>2248252</v>
       </c>
       <c r="E35" t="n">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="F35" t="n">
-        <v>2361010</v>
+        <v>2608798</v>
       </c>
       <c r="G35" t="n">
-        <v>13011</v>
+        <v>14216</v>
       </c>
       <c r="H35" t="n">
-        <v>15012551</v>
+        <v>16356799</v>
       </c>
       <c r="I35" t="n">
-        <v>12177993.76</v>
+        <v>13587590.76</v>
       </c>
       <c r="J35" t="n">
-        <v>3432431.19</v>
+        <v>3470460.19</v>
       </c>
       <c r="K35" t="n">
         <v>4919</v>
@@ -3095,48 +3223,48 @@
         <v>37281</v>
       </c>
       <c r="V35" t="n">
-        <v>41184</v>
+        <v>44498</v>
       </c>
       <c r="W35" t="n">
-        <v>5099</v>
+        <v>6963</v>
       </c>
       <c r="X35" t="n">
-        <v>3008721</v>
+        <v>4322419</v>
       </c>
       <c r="Y35" t="n">
-        <v>1826728.42855</v>
+        <v>2623377</v>
       </c>
       <c r="Z35" t="n">
-        <v>4846</v>
+        <v>8183</v>
       </c>
       <c r="AA35" t="n">
-        <v>4973888</v>
+        <v>7121531</v>
       </c>
       <c r="AB35" t="n">
-        <v>2057025</v>
+        <v>4030860</v>
       </c>
       <c r="AC35" t="n">
-        <v>25040</v>
+        <v>31629</v>
       </c>
       <c r="AD35" t="n">
-        <v>25756734</v>
+        <v>30847355</v>
       </c>
       <c r="AE35" t="n">
-        <v>18111084.18855</v>
+        <v>22534577.76</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.3566162538412163</v>
+        <v>0.338517657273295</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0.2327606086735259</v>
+        <v>0.2038042128963855</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -3158,39 +3286,43 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
-        <v>0.6470543475300425</v>
+        <v>0.6476545307822703</v>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="n">
-        <v>1.418000753515392</v>
+        <v>0.766752256342319</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="n">
-        <v>0.4221530711167286</v>
+        <v>0.3688898602198614</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>3248195.5</v>
+        <v>3588041.346153846</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>17899580.03846154</v>
+        <v>17484854.10344828</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>6941314.481481481</v>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>10061647.03703704</v>
+      </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -3202,17 +3334,17 @@
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
-        <v>4908965.842105263</v>
+        <v>4962777.37037037</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="n">
-        <v>8566140.444444444</v>
+        <v>12264858.94444444</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="n">
-        <v>34669110.26501124</v>
+        <v>45288074.68589842</v>
       </c>
     </row>
     <row r="39">
@@ -3220,7 +3352,9 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>400527</v>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -3280,7 +3414,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="n">
-        <v>92825644.41501124</v>
+        <v>103444608.8358984</v>
       </c>
     </row>
     <row r="41">
@@ -6245,7 +6379,7 @@
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
-        <v>3143221.071428571</v>
+        <v>2933673</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
@@ -6255,7 +6389,7 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="n">
-        <v>31360482.56779221</v>
+        <v>31150934.49636364</v>
       </c>
     </row>
     <row r="38">
@@ -6327,7 +6461,7 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="n">
-        <v>77885310.56779221</v>
+        <v>77675762.49636364</v>
       </c>
     </row>
     <row r="40">

--- a/snapshots/mkt_snapshot.xlsx
+++ b/snapshots/mkt_snapshot.xlsx
@@ -2880,9 +2880,15 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1441</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1858</v>
+      </c>
       <c r="W29" t="n">
         <v>1864</v>
       </c>
@@ -2902,13 +2908,13 @@
         <v>297136</v>
       </c>
       <c r="AC29" t="n">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AD29" t="n">
-        <v>2014185</v>
+        <v>2015626</v>
       </c>
       <c r="AE29" t="n">
-        <v>988375</v>
+        <v>990233</v>
       </c>
     </row>
     <row r="30">
@@ -2951,9 +2957,15 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>594</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2052</v>
+      </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
@@ -2961,13 +2973,13 @@
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AD30" t="n">
-        <v>516992</v>
+        <v>517586</v>
       </c>
       <c r="AE30" t="n">
-        <v>577714</v>
+        <v>579766</v>
       </c>
     </row>
     <row r="31">
@@ -3010,9 +3022,15 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1036</v>
+      </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -3026,7 +3044,7 @@
         <v>565165</v>
       </c>
       <c r="AE31" t="n">
-        <v>547796</v>
+        <v>548832</v>
       </c>
     </row>
     <row r="32">
@@ -3061,9 +3079,15 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1609</v>
+      </c>
+      <c r="V32" t="n">
+        <v>594</v>
+      </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
@@ -3071,13 +3095,13 @@
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AD32" t="n">
-        <v>93127</v>
+        <v>94736</v>
       </c>
       <c r="AE32" t="n">
-        <v>89783</v>
+        <v>90377</v>
       </c>
     </row>
     <row r="33">
@@ -3217,13 +3241,13 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="U35" t="n">
-        <v>37281</v>
+        <v>40925</v>
       </c>
       <c r="V35" t="n">
-        <v>44498</v>
+        <v>50038</v>
       </c>
       <c r="W35" t="n">
         <v>6963</v>
@@ -3244,13 +3268,13 @@
         <v>4030860</v>
       </c>
       <c r="AC35" t="n">
-        <v>31629</v>
+        <v>31633</v>
       </c>
       <c r="AD35" t="n">
-        <v>30847355</v>
+        <v>30850999</v>
       </c>
       <c r="AE35" t="n">
-        <v>22534577.76</v>
+        <v>22540117.76</v>
       </c>
     </row>
     <row r="36">
@@ -3296,7 +3320,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="n">
-        <v>0.3688898602198614</v>
+        <v>0.3687150763137804</v>
       </c>
     </row>
     <row r="38">
@@ -3329,7 +3353,7 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
-        <v>46228.44</v>
+        <v>50747</v>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
@@ -3344,7 +3368,7 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="n">
-        <v>45288074.68589842</v>
+        <v>45292593.24589842</v>
       </c>
     </row>
     <row r="39">
@@ -3414,7 +3438,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="n">
-        <v>103444608.8358984</v>
+        <v>103449127.3958984</v>
       </c>
     </row>
     <row r="41">

--- a/snapshots/mkt_snapshot.xlsx
+++ b/snapshots/mkt_snapshot.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="July'26" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="June'26" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="May'26" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="April'26" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Mar'26" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="FEB 26" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="JAN'26" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DEC'25" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Aug'26" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="July'26" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="June'26" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="May'26" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="April'26" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Mar'26" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="FEB 26" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="JAN'26" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="DEC'25" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE44"/>
+  <dimension ref="A1:AE35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,61 +657,49 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C3" t="n">
+        <v>109611</v>
+      </c>
+      <c r="D3" t="n">
         <v>122669</v>
       </c>
-      <c r="D3" t="n">
-        <v>79671</v>
-      </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>115165</v>
+        <v>98347</v>
       </c>
       <c r="G3" t="n">
-        <v>517</v>
+        <v>581</v>
       </c>
       <c r="H3" t="n">
+        <v>672725</v>
+      </c>
+      <c r="I3" t="n">
         <v>577913</v>
       </c>
-      <c r="I3" t="n">
-        <v>473887</v>
-      </c>
       <c r="J3" t="n">
-        <v>132988.62</v>
-      </c>
-      <c r="K3" t="n">
-        <v>174</v>
-      </c>
-      <c r="L3" t="n">
-        <v>207226</v>
-      </c>
-      <c r="M3" t="n">
-        <v>144194</v>
-      </c>
-      <c r="N3" t="n">
-        <v>331</v>
-      </c>
-      <c r="O3" t="n">
-        <v>335953</v>
-      </c>
-      <c r="P3" t="n">
-        <v>304169</v>
-      </c>
+        <v>105484</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>3504</v>
+        <v>2213</v>
       </c>
       <c r="V3" t="n">
         <v>338</v>
@@ -718,2159 +707,1067 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="n">
-        <v>216</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>200446</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>172188</v>
-      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>829</v>
+        <v>667</v>
       </c>
       <c r="AD3" t="n">
-        <v>904532</v>
+        <v>784549</v>
       </c>
       <c r="AE3" t="n">
-        <v>726084</v>
+        <v>700920</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46205</v>
+        <v>46236</v>
       </c>
       <c r="B4" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="C4" t="n">
+        <v>122663</v>
+      </c>
+      <c r="D4" t="n">
         <v>113015</v>
       </c>
-      <c r="D4" t="n">
-        <v>54694</v>
-      </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>67215</v>
-      </c>
-      <c r="G4" t="n">
-        <v>493</v>
-      </c>
-      <c r="H4" t="n">
-        <v>572665</v>
-      </c>
-      <c r="I4" t="n">
-        <v>487817</v>
-      </c>
-      <c r="J4" t="n">
-        <v>175655.4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>177</v>
-      </c>
-      <c r="L4" t="n">
-        <v>229723</v>
-      </c>
-      <c r="M4" t="n">
-        <v>121320</v>
-      </c>
-      <c r="N4" t="n">
-        <v>325</v>
-      </c>
-      <c r="O4" t="n">
-        <v>358668</v>
-      </c>
-      <c r="P4" t="n">
-        <v>351946</v>
-      </c>
+        <v>118438</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1746</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2574</v>
-      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
-        <v>184</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>164726</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>171334</v>
-      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>764</v>
+        <v>102</v>
       </c>
       <c r="AD4" t="n">
-        <v>852152</v>
+        <v>122663</v>
       </c>
       <c r="AE4" t="n">
-        <v>716419</v>
+        <v>113015</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46206</v>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="n">
-        <v>93624</v>
-      </c>
-      <c r="D5" t="n">
-        <v>70145</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>88327</v>
-      </c>
-      <c r="G5" t="n">
-        <v>401</v>
-      </c>
-      <c r="H5" t="n">
-        <v>494207</v>
-      </c>
-      <c r="I5" t="n">
-        <v>439498</v>
-      </c>
-      <c r="J5" t="n">
-        <v>160414.54</v>
-      </c>
-      <c r="K5" t="n">
-        <v>140</v>
-      </c>
-      <c r="L5" t="n">
-        <v>176339</v>
-      </c>
-      <c r="M5" t="n">
-        <v>145481</v>
-      </c>
-      <c r="N5" t="n">
-        <v>255</v>
-      </c>
-      <c r="O5" t="n">
-        <v>302641</v>
-      </c>
-      <c r="P5" t="n">
-        <v>361280</v>
-      </c>
+        <v>46237</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3179</v>
-      </c>
-      <c r="V5" t="n">
-        <v>2854</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>485</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>400877</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>120659</v>
-      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>991887</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>633156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B6" t="n">
-        <v>63</v>
-      </c>
-      <c r="C6" t="n">
-        <v>80265</v>
-      </c>
-      <c r="D6" t="n">
-        <v>63386</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>76454</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2096</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2325864</v>
-      </c>
-      <c r="I6" t="n">
-        <v>423491</v>
-      </c>
-      <c r="J6" t="n">
-        <v>472926.88</v>
-      </c>
-      <c r="K6" t="n">
-        <v>430</v>
-      </c>
-      <c r="L6" t="n">
-        <v>520937</v>
-      </c>
-      <c r="M6" t="n">
-        <v>144955</v>
-      </c>
-      <c r="N6" t="n">
-        <v>763</v>
-      </c>
-      <c r="O6" t="n">
-        <v>807624</v>
-      </c>
-      <c r="P6" t="n">
-        <v>271743</v>
-      </c>
+        <v>46238</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>3133</v>
-      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="n">
-        <v>654</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>553605</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>93565</v>
-      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>2813</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2959734</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>583575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46208</v>
-      </c>
-      <c r="B7" t="n">
-        <v>71</v>
-      </c>
-      <c r="C7" t="n">
-        <v>97890</v>
-      </c>
-      <c r="D7" t="n">
-        <v>63007</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="n">
-        <v>94854</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1325</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1469886</v>
-      </c>
-      <c r="I7" t="n">
-        <v>466957</v>
-      </c>
-      <c r="J7" t="n">
-        <v>342859.67</v>
-      </c>
-      <c r="K7" t="n">
-        <v>488</v>
-      </c>
-      <c r="L7" t="n">
-        <v>534046</v>
-      </c>
-      <c r="M7" t="n">
-        <v>157104</v>
-      </c>
-      <c r="N7" t="n">
-        <v>583</v>
-      </c>
-      <c r="O7" t="n">
-        <v>616202</v>
-      </c>
-      <c r="P7" t="n">
-        <v>266991</v>
-      </c>
+        <v>46239</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1314</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1395</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1368</v>
-      </c>
-      <c r="X7" t="n">
-        <v>762491</v>
-      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="n">
-        <v>516</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>443244</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>88972</v>
-      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>3283</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2774825</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>620331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46209</v>
-      </c>
-      <c r="B8" t="n">
-        <v>114</v>
-      </c>
-      <c r="C8" t="n">
-        <v>130411</v>
-      </c>
-      <c r="D8" t="n">
-        <v>55939</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>97672</v>
-      </c>
-      <c r="G8" t="n">
-        <v>664</v>
-      </c>
-      <c r="H8" t="n">
-        <v>750089</v>
-      </c>
-      <c r="I8" t="n">
-        <v>497076</v>
-      </c>
-      <c r="J8" t="n">
-        <v>74490.58</v>
-      </c>
-      <c r="K8" t="n">
-        <v>198</v>
-      </c>
-      <c r="L8" t="n">
-        <v>234077</v>
-      </c>
-      <c r="M8" t="n">
-        <v>162173</v>
-      </c>
-      <c r="N8" t="n">
-        <v>477</v>
-      </c>
-      <c r="O8" t="n">
-        <v>498727</v>
-      </c>
-      <c r="P8" t="n">
-        <v>350312</v>
-      </c>
+        <v>46240</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2100</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4640</v>
-      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="n">
-        <v>335</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>294197</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>221739</v>
-      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>1115</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1176797</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>779394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="B9" t="n">
-        <v>105</v>
-      </c>
-      <c r="C9" t="n">
-        <v>151629</v>
-      </c>
-      <c r="D9" t="n">
-        <v>85529</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="n">
-        <v>145718</v>
-      </c>
-      <c r="G9" t="n">
-        <v>321</v>
-      </c>
-      <c r="H9" t="n">
-        <v>340411</v>
-      </c>
-      <c r="I9" t="n">
-        <v>492445</v>
-      </c>
-      <c r="J9" t="n">
-        <v>35484</v>
-      </c>
-      <c r="K9" t="n">
-        <v>183</v>
-      </c>
-      <c r="L9" t="n">
-        <v>269863</v>
-      </c>
-      <c r="M9" t="n">
-        <v>147137</v>
-      </c>
-      <c r="N9" t="n">
-        <v>236</v>
-      </c>
-      <c r="O9" t="n">
-        <v>274777</v>
-      </c>
-      <c r="P9" t="n">
-        <v>323717</v>
-      </c>
+        <v>46241</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1219</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="n">
-        <v>778209</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>422</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>383929</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>168924</v>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>877188</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1525107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="B10" t="n">
-        <v>106</v>
-      </c>
-      <c r="C10" t="n">
-        <v>138616</v>
-      </c>
-      <c r="D10" t="n">
-        <v>51205</v>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>119191</v>
-      </c>
-      <c r="G10" t="n">
-        <v>295</v>
-      </c>
-      <c r="H10" t="n">
-        <v>367286</v>
-      </c>
-      <c r="I10" t="n">
-        <v>415092</v>
-      </c>
-      <c r="J10" t="n">
-        <v>131794</v>
-      </c>
-      <c r="K10" t="n">
-        <v>296</v>
-      </c>
-      <c r="L10" t="n">
-        <v>340606</v>
-      </c>
-      <c r="M10" t="n">
-        <v>142242</v>
-      </c>
-      <c r="N10" t="n">
-        <v>245</v>
-      </c>
-      <c r="O10" t="n">
-        <v>286640</v>
-      </c>
-      <c r="P10" t="n">
-        <v>263834</v>
-      </c>
+        <v>46242</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1986</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="n">
-        <v>347</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>289885</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>86788</v>
-      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>751</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>797773</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>553085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="B11" t="n">
-        <v>93</v>
-      </c>
-      <c r="C11" t="n">
-        <v>108026</v>
-      </c>
-      <c r="D11" t="n">
-        <v>91198</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>95748</v>
-      </c>
-      <c r="G11" t="n">
-        <v>329</v>
-      </c>
-      <c r="H11" t="n">
-        <v>389610</v>
-      </c>
-      <c r="I11" t="n">
-        <v>482786</v>
-      </c>
-      <c r="J11" t="n">
-        <v>138130.58</v>
-      </c>
-      <c r="K11" t="n">
-        <v>157</v>
-      </c>
-      <c r="L11" t="n">
-        <v>180434</v>
-      </c>
-      <c r="M11" t="n">
-        <v>143004</v>
-      </c>
-      <c r="N11" t="n">
-        <v>244</v>
-      </c>
-      <c r="O11" t="n">
-        <v>277603</v>
-      </c>
-      <c r="P11" t="n">
-        <v>329236</v>
-      </c>
+        <v>46243</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1317</v>
-      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="n">
-        <v>313</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>259659</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>87491</v>
-      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>735</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>757295</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>662792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B12" t="n">
-        <v>77</v>
-      </c>
-      <c r="C12" t="n">
-        <v>96054</v>
-      </c>
-      <c r="D12" t="n">
-        <v>62903</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>77493</v>
-      </c>
-      <c r="G12" t="n">
-        <v>338</v>
-      </c>
-      <c r="H12" t="n">
-        <v>405417</v>
-      </c>
-      <c r="I12" t="n">
-        <v>472575</v>
-      </c>
-      <c r="J12" t="n">
-        <v>126605.85</v>
-      </c>
-      <c r="K12" t="n">
-        <v>294</v>
-      </c>
-      <c r="L12" t="n">
-        <v>320989</v>
-      </c>
-      <c r="M12" t="n">
-        <v>165125</v>
-      </c>
-      <c r="N12" t="n">
-        <v>229</v>
-      </c>
-      <c r="O12" t="n">
-        <v>257874</v>
-      </c>
-      <c r="P12" t="n">
-        <v>287107</v>
-      </c>
+        <v>46244</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1701</v>
-      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="n">
-        <v>243</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>213247</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>110027</v>
-      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>714718</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>647206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46214</v>
-      </c>
-      <c r="B13" t="n">
-        <v>83</v>
-      </c>
-      <c r="C13" t="n">
-        <v>111959</v>
-      </c>
-      <c r="D13" t="n">
-        <v>59986</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" t="n">
-        <v>106955</v>
-      </c>
-      <c r="G13" t="n">
-        <v>515</v>
-      </c>
-      <c r="H13" t="n">
-        <v>601531</v>
-      </c>
-      <c r="I13" t="n">
-        <v>421187</v>
-      </c>
-      <c r="J13" t="n">
-        <v>146738</v>
-      </c>
-      <c r="K13" t="n">
-        <v>236</v>
-      </c>
-      <c r="L13" t="n">
-        <v>282533</v>
-      </c>
-      <c r="M13" t="n">
-        <v>172993</v>
-      </c>
-      <c r="N13" t="n">
-        <v>279</v>
-      </c>
-      <c r="O13" t="n">
-        <v>315998</v>
-      </c>
-      <c r="P13" t="n">
-        <v>295520</v>
-      </c>
+        <v>46245</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>585</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="n">
-        <v>556</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>461033</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>104409</v>
-      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>1155</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1175108</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>585582</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="B14" t="n">
-        <v>89</v>
-      </c>
-      <c r="C14" t="n">
-        <v>109047</v>
-      </c>
-      <c r="D14" t="n">
-        <v>62687</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" t="n">
-        <v>104193</v>
-      </c>
-      <c r="G14" t="n">
-        <v>415</v>
-      </c>
-      <c r="H14" t="n">
-        <v>472849</v>
-      </c>
-      <c r="I14" t="n">
-        <v>455364</v>
-      </c>
-      <c r="J14" t="n">
-        <v>110359</v>
-      </c>
-      <c r="K14" t="n">
-        <v>147</v>
-      </c>
-      <c r="L14" t="n">
-        <v>181952</v>
-      </c>
-      <c r="M14" t="n">
-        <v>136625</v>
-      </c>
-      <c r="N14" t="n">
-        <v>268</v>
-      </c>
-      <c r="O14" t="n">
-        <v>290897</v>
-      </c>
-      <c r="P14" t="n">
-        <v>299984</v>
-      </c>
+        <v>46246</v>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="n">
-        <v>5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4000</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2269</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1275288</v>
-      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="n">
-        <v>470</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>390853</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>151404</v>
-      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>3248</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2252037</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>669455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="B15" t="n">
-        <v>98</v>
-      </c>
-      <c r="C15" t="n">
-        <v>137076</v>
-      </c>
-      <c r="D15" t="n">
-        <v>47998</v>
-      </c>
-      <c r="E15" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" t="n">
-        <v>129174</v>
-      </c>
-      <c r="G15" t="n">
-        <v>290</v>
-      </c>
-      <c r="H15" t="n">
-        <v>333657</v>
-      </c>
-      <c r="I15" t="n">
-        <v>446808</v>
-      </c>
-      <c r="J15" t="n">
-        <v>75122</v>
-      </c>
-      <c r="K15" t="n">
-        <v>140</v>
-      </c>
-      <c r="L15" t="n">
-        <v>168950</v>
-      </c>
-      <c r="M15" t="n">
-        <v>135260</v>
-      </c>
-      <c r="N15" t="n">
-        <v>210</v>
-      </c>
-      <c r="O15" t="n">
-        <v>235857</v>
-      </c>
-      <c r="P15" t="n">
-        <v>309024</v>
-      </c>
+        <v>46247</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>680</v>
-      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="n">
-        <v>199</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>169440</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>194876</v>
-      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>587</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>640173</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>690362</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B16" t="n">
-        <v>79</v>
-      </c>
-      <c r="C16" t="n">
-        <v>118795</v>
-      </c>
-      <c r="D16" t="n">
-        <v>55177</v>
-      </c>
-      <c r="E16" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>72662</v>
-      </c>
-      <c r="G16" t="n">
-        <v>291</v>
-      </c>
-      <c r="H16" t="n">
-        <v>337291</v>
-      </c>
-      <c r="I16" t="n">
-        <v>534224</v>
-      </c>
-      <c r="J16" t="n">
-        <v>96462</v>
-      </c>
-      <c r="K16" t="n">
-        <v>155</v>
-      </c>
-      <c r="L16" t="n">
-        <v>190758</v>
-      </c>
-      <c r="M16" t="n">
-        <v>186516</v>
-      </c>
-      <c r="N16" t="n">
-        <v>216</v>
-      </c>
-      <c r="O16" t="n">
-        <v>235075</v>
-      </c>
-      <c r="P16" t="n">
-        <v>349541</v>
-      </c>
+        <v>46248</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1560</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2789</v>
-      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="n">
-        <v>613268</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>212</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>189358</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>180051</v>
-      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>647004</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1385509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="B17" t="n">
-        <v>80</v>
-      </c>
-      <c r="C17" t="n">
-        <v>101507</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80340</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>95372</v>
-      </c>
-      <c r="G17" t="n">
-        <v>271</v>
-      </c>
-      <c r="H17" t="n">
-        <v>321147</v>
-      </c>
-      <c r="I17" t="n">
-        <v>423259</v>
-      </c>
-      <c r="J17" t="n">
-        <v>71541.95</v>
-      </c>
-      <c r="K17" t="n">
-        <v>138</v>
-      </c>
-      <c r="L17" t="n">
-        <v>172090</v>
-      </c>
-      <c r="M17" t="n">
-        <v>159713</v>
-      </c>
-      <c r="N17" t="n">
-        <v>220</v>
-      </c>
-      <c r="O17" t="n">
-        <v>234439</v>
-      </c>
-      <c r="P17" t="n">
-        <v>252176</v>
-      </c>
+        <v>46249</v>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2290</v>
-      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="n">
-        <v>185</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>191616</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>104598</v>
-      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>536</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>614270</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>610487</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="B18" t="n">
-        <v>61</v>
-      </c>
-      <c r="C18" t="n">
-        <v>78711</v>
-      </c>
-      <c r="D18" t="n">
-        <v>129196</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>54470</v>
-      </c>
-      <c r="G18" t="n">
-        <v>334</v>
-      </c>
-      <c r="H18" t="n">
-        <v>398349</v>
-      </c>
-      <c r="I18" t="n">
-        <v>429308</v>
-      </c>
-      <c r="J18" t="n">
-        <v>75000.03999999999</v>
-      </c>
-      <c r="K18" t="n">
-        <v>80</v>
-      </c>
-      <c r="L18" t="n">
-        <v>113356</v>
-      </c>
-      <c r="M18" t="n">
-        <v>128819</v>
-      </c>
-      <c r="N18" t="n">
-        <v>254</v>
-      </c>
-      <c r="O18" t="n">
-        <v>284993</v>
-      </c>
-      <c r="P18" t="n">
-        <v>308649</v>
-      </c>
+        <v>46250</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2861</v>
-      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="n">
-        <v>197</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>163403</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>125511</v>
-      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>640463</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>686876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="B19" t="n">
-        <v>64</v>
-      </c>
-      <c r="C19" t="n">
-        <v>69627</v>
-      </c>
-      <c r="D19" t="n">
-        <v>102617</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>65972</v>
-      </c>
-      <c r="G19" t="n">
-        <v>333</v>
-      </c>
-      <c r="H19" t="n">
-        <v>392774</v>
-      </c>
-      <c r="I19" t="n">
-        <v>537858</v>
-      </c>
-      <c r="J19" t="n">
-        <v>132687</v>
-      </c>
-      <c r="K19" t="n">
-        <v>91</v>
-      </c>
-      <c r="L19" t="n">
-        <v>126372</v>
-      </c>
-      <c r="M19" t="n">
-        <v>191576</v>
-      </c>
-      <c r="N19" t="n">
-        <v>242</v>
-      </c>
-      <c r="O19" t="n">
-        <v>266402</v>
-      </c>
-      <c r="P19" t="n">
-        <v>348862</v>
-      </c>
+        <v>46251</v>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1640</v>
-      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="n">
-        <v>166</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>142420</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>139950</v>
-      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>604821</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>782065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="B20" t="n">
-        <v>35</v>
-      </c>
-      <c r="C20" t="n">
-        <v>48665</v>
-      </c>
-      <c r="D20" t="n">
-        <v>107604</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>46762</v>
-      </c>
-      <c r="G20" t="n">
-        <v>380</v>
-      </c>
-      <c r="H20" t="n">
-        <v>450065</v>
-      </c>
-      <c r="I20" t="n">
-        <v>536567</v>
-      </c>
-      <c r="J20" t="n">
-        <v>126818.18</v>
-      </c>
-      <c r="K20" t="n">
-        <v>102</v>
-      </c>
-      <c r="L20" t="n">
-        <v>136392</v>
-      </c>
-      <c r="M20" t="n">
-        <v>209260</v>
-      </c>
-      <c r="N20" t="n">
-        <v>278</v>
-      </c>
-      <c r="O20" t="n">
-        <v>313673</v>
-      </c>
-      <c r="P20" t="n">
-        <v>331962</v>
-      </c>
+        <v>46252</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1611</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="n">
-        <v>391</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>344341</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>100984</v>
-      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>807</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>844682</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>745155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="B21" t="n">
-        <v>68</v>
-      </c>
-      <c r="C21" t="n">
-        <v>77794</v>
-      </c>
-      <c r="D21" t="n">
-        <v>49794</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>73921</v>
-      </c>
-      <c r="G21" t="n">
-        <v>467</v>
-      </c>
-      <c r="H21" t="n">
-        <v>540776</v>
-      </c>
-      <c r="I21" t="n">
-        <v>431154</v>
-      </c>
-      <c r="J21" t="n">
-        <v>144160.25</v>
-      </c>
-      <c r="K21" t="n">
-        <v>133</v>
-      </c>
-      <c r="L21" t="n">
-        <v>162475</v>
-      </c>
-      <c r="M21" t="n">
-        <v>172468</v>
-      </c>
-      <c r="N21" t="n">
-        <v>334</v>
-      </c>
-      <c r="O21" t="n">
-        <v>378301</v>
-      </c>
-      <c r="P21" t="n">
-        <v>263816</v>
-      </c>
+        <v>46253</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1457</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4539</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1462</v>
-      </c>
-      <c r="X21" t="n">
-        <v>970942</v>
-      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="n">
-        <v>389</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>328924</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>122410</v>
-      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>2388</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1919893</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>607897</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B22" t="n">
-        <v>68</v>
-      </c>
-      <c r="C22" t="n">
-        <v>118249</v>
-      </c>
-      <c r="D22" t="n">
-        <v>69240</v>
-      </c>
-      <c r="E22" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" t="n">
-        <v>108897</v>
-      </c>
-      <c r="G22" t="n">
-        <v>360</v>
-      </c>
-      <c r="H22" t="n">
-        <v>485773</v>
-      </c>
-      <c r="I22" t="n">
-        <v>462080</v>
-      </c>
-      <c r="J22" t="n">
-        <v>126866.73</v>
-      </c>
-      <c r="K22" t="n">
-        <v>180</v>
-      </c>
-      <c r="L22" t="n">
-        <v>241684</v>
-      </c>
-      <c r="M22" t="n">
-        <v>185709</v>
-      </c>
-      <c r="N22" t="n">
-        <v>205</v>
-      </c>
-      <c r="O22" t="n">
-        <v>245499</v>
-      </c>
-      <c r="P22" t="n">
-        <v>282791</v>
-      </c>
+        <v>46254</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>851</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="n">
-        <v>172</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>130392</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>191253</v>
-      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>601</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>735265</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>722573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B23" t="n">
-        <v>66</v>
-      </c>
-      <c r="C23" t="n">
-        <v>100508</v>
-      </c>
-      <c r="D23" t="n">
-        <v>57008</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>71561</v>
-      </c>
-      <c r="G23" t="n">
-        <v>389</v>
-      </c>
-      <c r="H23" t="n">
-        <v>472792</v>
-      </c>
-      <c r="I23" t="n">
-        <v>483531</v>
-      </c>
-      <c r="J23" t="n">
-        <v>125305.89</v>
-      </c>
-      <c r="K23" t="n">
-        <v>227</v>
-      </c>
-      <c r="L23" t="n">
-        <v>301973</v>
-      </c>
-      <c r="M23" t="n">
-        <v>156406</v>
-      </c>
-      <c r="N23" t="n">
-        <v>248</v>
-      </c>
-      <c r="O23" t="n">
-        <v>280214</v>
-      </c>
-      <c r="P23" t="n">
-        <v>333204</v>
-      </c>
+        <v>46255</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>607</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="n">
-        <v>609352</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>137</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>112685</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>174970</v>
-      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>686592</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1324861</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="B24" t="n">
-        <v>54</v>
-      </c>
-      <c r="C24" t="n">
-        <v>63449</v>
-      </c>
-      <c r="D24" t="n">
-        <v>79811</v>
-      </c>
-      <c r="E24" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" t="n">
-        <v>58298</v>
-      </c>
-      <c r="G24" t="n">
-        <v>396</v>
-      </c>
-      <c r="H24" t="n">
-        <v>449824</v>
-      </c>
-      <c r="I24" t="n">
-        <v>426383</v>
-      </c>
-      <c r="J24" t="n">
-        <v>75734.33</v>
-      </c>
-      <c r="K24" t="n">
-        <v>179</v>
-      </c>
-      <c r="L24" t="n">
-        <v>211755</v>
-      </c>
-      <c r="M24" t="n">
-        <v>148967</v>
-      </c>
-      <c r="N24" t="n">
-        <v>263</v>
-      </c>
-      <c r="O24" t="n">
-        <v>290691</v>
-      </c>
-      <c r="P24" t="n">
-        <v>276298</v>
-      </c>
+        <v>46256</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2313</v>
-      </c>
-      <c r="V24" t="n">
-        <v>853</v>
-      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="n">
-        <v>103758</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>151</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>131461</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>141505</v>
-      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>647047</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>752310</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="B25" t="n">
-        <v>62</v>
-      </c>
-      <c r="C25" t="n">
-        <v>100526</v>
-      </c>
-      <c r="D25" t="n">
-        <v>68547</v>
-      </c>
-      <c r="E25" t="n">
-        <v>8</v>
-      </c>
-      <c r="F25" t="n">
-        <v>86807</v>
-      </c>
-      <c r="G25" t="n">
-        <v>435</v>
-      </c>
-      <c r="H25" t="n">
-        <v>501457</v>
-      </c>
-      <c r="I25" t="n">
-        <v>506643.76</v>
-      </c>
-      <c r="J25" t="n">
-        <v>108754.3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>179</v>
-      </c>
-      <c r="L25" t="n">
-        <v>230832</v>
-      </c>
-      <c r="M25" t="n">
-        <v>172007</v>
-      </c>
-      <c r="N25" t="n">
-        <v>286</v>
-      </c>
-      <c r="O25" t="n">
-        <v>293352</v>
-      </c>
-      <c r="P25" t="n">
-        <v>323498</v>
-      </c>
+        <v>46257</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2316</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5029</v>
-      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="n">
-        <v>103758</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>202</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>190620</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>123916</v>
-      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>701</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>794919</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>807893.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B26" t="n">
-        <v>64</v>
-      </c>
-      <c r="C26" t="n">
-        <v>89889</v>
-      </c>
-      <c r="D26" t="n">
-        <v>75711</v>
-      </c>
-      <c r="E26" t="n">
-        <v>6</v>
-      </c>
-      <c r="F26" t="n">
-        <v>52678</v>
-      </c>
-      <c r="G26" t="n">
-        <v>357</v>
-      </c>
-      <c r="H26" t="n">
-        <v>404215</v>
-      </c>
-      <c r="I26" t="n">
-        <v>506555</v>
-      </c>
-      <c r="J26" t="n">
-        <v>32875.25</v>
-      </c>
-      <c r="K26" t="n">
-        <v>132</v>
-      </c>
-      <c r="L26" t="n">
-        <v>167691</v>
-      </c>
-      <c r="M26" t="n">
-        <v>171436</v>
-      </c>
-      <c r="N26" t="n">
-        <v>247</v>
-      </c>
-      <c r="O26" t="n">
-        <v>273597</v>
-      </c>
-      <c r="P26" t="n">
-        <v>331583</v>
-      </c>
+        <v>46258</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2508</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1007</v>
-      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="n">
-        <v>103758</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>186</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>174329</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>119763</v>
-      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>609</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>670941</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>806794</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46228</v>
-      </c>
-      <c r="B27" t="n">
-        <v>54</v>
-      </c>
-      <c r="C27" t="n">
-        <v>59046</v>
-      </c>
-      <c r="D27" t="n">
-        <v>61126</v>
-      </c>
-      <c r="E27" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" t="n">
-        <v>56616</v>
-      </c>
-      <c r="G27" t="n">
-        <v>466</v>
-      </c>
-      <c r="H27" t="n">
-        <v>543034</v>
-      </c>
-      <c r="I27" t="n">
-        <v>491482</v>
-      </c>
-      <c r="J27" t="n">
-        <v>70850.44</v>
-      </c>
-      <c r="K27" t="n">
-        <v>133</v>
-      </c>
-      <c r="L27" t="n">
-        <v>176129</v>
-      </c>
-      <c r="M27" t="n">
-        <v>129972</v>
-      </c>
-      <c r="N27" t="n">
-        <v>339</v>
-      </c>
-      <c r="O27" t="n">
-        <v>369336</v>
-      </c>
-      <c r="P27" t="n">
-        <v>354744</v>
-      </c>
+        <v>46259</v>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="n">
-        <v>4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>4425</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1544</v>
-      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="n">
-        <v>103758</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>350</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>333052</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>241915</v>
-      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>874</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>939557</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>899825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B28" t="n">
-        <v>88</v>
-      </c>
-      <c r="C28" t="n">
-        <v>133334</v>
-      </c>
-      <c r="D28" t="n">
-        <v>70556</v>
-      </c>
-      <c r="E28" t="n">
-        <v>9</v>
-      </c>
-      <c r="F28" t="n">
-        <v>127998</v>
-      </c>
-      <c r="G28" t="n">
-        <v>533</v>
-      </c>
-      <c r="H28" t="n">
-        <v>613669</v>
-      </c>
-      <c r="I28" t="n">
-        <v>433966</v>
-      </c>
-      <c r="J28" t="n">
-        <v>121805.71</v>
-      </c>
-      <c r="K28" t="n">
-        <v>130</v>
-      </c>
-      <c r="L28" t="n">
-        <v>166479</v>
-      </c>
-      <c r="M28" t="n">
-        <v>123303</v>
-      </c>
-      <c r="N28" t="n">
-        <v>398</v>
-      </c>
-      <c r="O28" t="n">
-        <v>438337</v>
-      </c>
-      <c r="P28" t="n">
-        <v>283140</v>
-      </c>
+        <v>46260</v>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>3314</v>
-      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="n">
-        <v>103758</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>312</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>291210</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>194522</v>
-      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>933</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1038213</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>806116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B29" t="n">
-        <v>53</v>
-      </c>
-      <c r="C29" t="n">
-        <v>73912</v>
-      </c>
-      <c r="D29" t="n">
-        <v>153078</v>
-      </c>
-      <c r="E29" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" t="n">
-        <v>70837</v>
-      </c>
-      <c r="G29" t="n">
-        <v>397</v>
-      </c>
-      <c r="H29" t="n">
-        <v>453996</v>
-      </c>
-      <c r="I29" t="n">
-        <v>434403</v>
-      </c>
-      <c r="J29" t="n">
-        <v>38029</v>
-      </c>
+        <v>46261</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -2880,74 +1777,38 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="n">
-        <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1441</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1858</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1864</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1313698</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>103758</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>193</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>172579</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>297136</v>
-      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>2509</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2015626</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>990233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="B30" t="n">
-        <v>66</v>
-      </c>
-      <c r="C30" t="n">
-        <v>85641</v>
-      </c>
-      <c r="D30" t="n">
-        <v>60533</v>
-      </c>
-      <c r="E30" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" t="n">
-        <v>59797</v>
-      </c>
-      <c r="G30" t="n">
-        <v>395</v>
-      </c>
-      <c r="H30" t="n">
-        <v>431351</v>
-      </c>
-      <c r="I30" t="n">
-        <v>517181</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
+        <v>46262</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -2957,15 +1818,9 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>594</v>
-      </c>
-      <c r="V30" t="n">
-        <v>2052</v>
-      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
@@ -2973,46 +1828,28 @@
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>517586</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>579766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="B31" t="n">
-        <v>63</v>
-      </c>
-      <c r="C31" t="n">
-        <v>106264</v>
-      </c>
-      <c r="D31" t="n">
-        <v>89783</v>
-      </c>
-      <c r="E31" t="n">
-        <v>11</v>
-      </c>
-      <c r="F31" t="n">
-        <v>101469</v>
-      </c>
-      <c r="G31" t="n">
-        <v>413</v>
-      </c>
-      <c r="H31" t="n">
-        <v>458901</v>
-      </c>
-      <c r="I31" t="n">
-        <v>458013</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
+        <v>46263</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -3022,15 +1859,9 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1036</v>
-      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -3038,34 +1869,24 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>565165</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>548832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="B32" t="n">
-        <v>54</v>
-      </c>
-      <c r="C32" t="n">
-        <v>93127</v>
-      </c>
-      <c r="D32" t="n">
-        <v>89783</v>
-      </c>
-      <c r="E32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F32" t="n">
-        <v>86522</v>
-      </c>
+        <v>46264</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -3079,15 +1900,9 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1609</v>
-      </c>
-      <c r="V32" t="n">
-        <v>594</v>
-      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
@@ -3095,18 +1910,18 @@
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>94736</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>90377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
@@ -3140,6 +1955,2918 @@
       </c>
       <c r="AD33" t="n">
         <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>185</v>
+      </c>
+      <c r="C34" t="n">
+        <v>232274</v>
+      </c>
+      <c r="D34" t="n">
+        <v>235684</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" t="n">
+        <v>216785</v>
+      </c>
+      <c r="G34" t="n">
+        <v>581</v>
+      </c>
+      <c r="H34" t="n">
+        <v>672725</v>
+      </c>
+      <c r="I34" t="n">
+        <v>577913</v>
+      </c>
+      <c r="J34" t="n">
+        <v>105484</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2213</v>
+      </c>
+      <c r="V34" t="n">
+        <v>338</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>769</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>907212</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>813935</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>-0.01446852565299299</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>0.1640592961224267</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>#DIV/0! (Function DIVIDE parameter 2 cannot be zero.)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>#DIV/0! (Function DIVIDE parameter 2 cannot be zero.)</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>#DIV/0! (Function DIVIDE parameter 2 cannot be zero.)</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>#DIV/0! (Function DIVIDE parameter 2 cannot be zero.)</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="n">
+        <v>0.1146000602013674</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AE44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Shopify</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Amazon Core</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Amazon NOW + Fresh</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>xx</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Flipkart</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Minutes</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>First Club</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LM GMV</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Dolchi</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Total Sale</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>LM GMV</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>AD sales</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>LM GMV</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>LM GMV</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>LM GMV</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>LM GMV</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>LM GMV</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>LM GMV</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>LM GMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3" t="n">
+        <v>122669</v>
+      </c>
+      <c r="D3" t="n">
+        <v>79671</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>115165</v>
+      </c>
+      <c r="G3" t="n">
+        <v>517</v>
+      </c>
+      <c r="H3" t="n">
+        <v>577913</v>
+      </c>
+      <c r="I3" t="n">
+        <v>473887</v>
+      </c>
+      <c r="J3" t="n">
+        <v>132988.62</v>
+      </c>
+      <c r="K3" t="n">
+        <v>174</v>
+      </c>
+      <c r="L3" t="n">
+        <v>207226</v>
+      </c>
+      <c r="M3" t="n">
+        <v>144194</v>
+      </c>
+      <c r="N3" t="n">
+        <v>331</v>
+      </c>
+      <c r="O3" t="n">
+        <v>335953</v>
+      </c>
+      <c r="P3" t="n">
+        <v>304169</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3504</v>
+      </c>
+      <c r="V3" t="n">
+        <v>338</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>216</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>200446</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>172188</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>829</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>904532</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>726084</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B4" t="n">
+        <v>85</v>
+      </c>
+      <c r="C4" t="n">
+        <v>113015</v>
+      </c>
+      <c r="D4" t="n">
+        <v>54694</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>67215</v>
+      </c>
+      <c r="G4" t="n">
+        <v>493</v>
+      </c>
+      <c r="H4" t="n">
+        <v>572665</v>
+      </c>
+      <c r="I4" t="n">
+        <v>487817</v>
+      </c>
+      <c r="J4" t="n">
+        <v>175655.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>177</v>
+      </c>
+      <c r="L4" t="n">
+        <v>229723</v>
+      </c>
+      <c r="M4" t="n">
+        <v>121320</v>
+      </c>
+      <c r="N4" t="n">
+        <v>325</v>
+      </c>
+      <c r="O4" t="n">
+        <v>358668</v>
+      </c>
+      <c r="P4" t="n">
+        <v>351946</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1746</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2574</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>184</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>164726</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>171334</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>764</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>852152</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>716419</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="n">
+        <v>93624</v>
+      </c>
+      <c r="D5" t="n">
+        <v>70145</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>88327</v>
+      </c>
+      <c r="G5" t="n">
+        <v>401</v>
+      </c>
+      <c r="H5" t="n">
+        <v>494207</v>
+      </c>
+      <c r="I5" t="n">
+        <v>439498</v>
+      </c>
+      <c r="J5" t="n">
+        <v>160414.54</v>
+      </c>
+      <c r="K5" t="n">
+        <v>140</v>
+      </c>
+      <c r="L5" t="n">
+        <v>176339</v>
+      </c>
+      <c r="M5" t="n">
+        <v>145481</v>
+      </c>
+      <c r="N5" t="n">
+        <v>255</v>
+      </c>
+      <c r="O5" t="n">
+        <v>302641</v>
+      </c>
+      <c r="P5" t="n">
+        <v>361280</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3179</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2854</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>485</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>400877</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>120659</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>960</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>991887</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>633156</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B6" t="n">
+        <v>63</v>
+      </c>
+      <c r="C6" t="n">
+        <v>80265</v>
+      </c>
+      <c r="D6" t="n">
+        <v>63386</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>76454</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2096</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2325864</v>
+      </c>
+      <c r="I6" t="n">
+        <v>423491</v>
+      </c>
+      <c r="J6" t="n">
+        <v>472926.88</v>
+      </c>
+      <c r="K6" t="n">
+        <v>430</v>
+      </c>
+      <c r="L6" t="n">
+        <v>520937</v>
+      </c>
+      <c r="M6" t="n">
+        <v>144955</v>
+      </c>
+      <c r="N6" t="n">
+        <v>763</v>
+      </c>
+      <c r="O6" t="n">
+        <v>807624</v>
+      </c>
+      <c r="P6" t="n">
+        <v>271743</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3133</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>654</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>553605</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>93565</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2813</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2959734</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>583575</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C7" t="n">
+        <v>97890</v>
+      </c>
+      <c r="D7" t="n">
+        <v>63007</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>94854</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1325</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1469886</v>
+      </c>
+      <c r="I7" t="n">
+        <v>466957</v>
+      </c>
+      <c r="J7" t="n">
+        <v>342859.67</v>
+      </c>
+      <c r="K7" t="n">
+        <v>488</v>
+      </c>
+      <c r="L7" t="n">
+        <v>534046</v>
+      </c>
+      <c r="M7" t="n">
+        <v>157104</v>
+      </c>
+      <c r="N7" t="n">
+        <v>583</v>
+      </c>
+      <c r="O7" t="n">
+        <v>616202</v>
+      </c>
+      <c r="P7" t="n">
+        <v>266991</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1314</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1395</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1368</v>
+      </c>
+      <c r="X7" t="n">
+        <v>762491</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>516</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>443244</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>88972</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3283</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2774825</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>620331</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B8" t="n">
+        <v>114</v>
+      </c>
+      <c r="C8" t="n">
+        <v>130411</v>
+      </c>
+      <c r="D8" t="n">
+        <v>55939</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>97672</v>
+      </c>
+      <c r="G8" t="n">
+        <v>664</v>
+      </c>
+      <c r="H8" t="n">
+        <v>750089</v>
+      </c>
+      <c r="I8" t="n">
+        <v>497076</v>
+      </c>
+      <c r="J8" t="n">
+        <v>74490.58</v>
+      </c>
+      <c r="K8" t="n">
+        <v>198</v>
+      </c>
+      <c r="L8" t="n">
+        <v>234077</v>
+      </c>
+      <c r="M8" t="n">
+        <v>162173</v>
+      </c>
+      <c r="N8" t="n">
+        <v>477</v>
+      </c>
+      <c r="O8" t="n">
+        <v>498727</v>
+      </c>
+      <c r="P8" t="n">
+        <v>350312</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2100</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4640</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>335</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>294197</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>221739</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1115</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1176797</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>779394</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B9" t="n">
+        <v>105</v>
+      </c>
+      <c r="C9" t="n">
+        <v>151629</v>
+      </c>
+      <c r="D9" t="n">
+        <v>85529</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>145718</v>
+      </c>
+      <c r="G9" t="n">
+        <v>321</v>
+      </c>
+      <c r="H9" t="n">
+        <v>340411</v>
+      </c>
+      <c r="I9" t="n">
+        <v>492445</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35484</v>
+      </c>
+      <c r="K9" t="n">
+        <v>183</v>
+      </c>
+      <c r="L9" t="n">
+        <v>269863</v>
+      </c>
+      <c r="M9" t="n">
+        <v>147137</v>
+      </c>
+      <c r="N9" t="n">
+        <v>236</v>
+      </c>
+      <c r="O9" t="n">
+        <v>274777</v>
+      </c>
+      <c r="P9" t="n">
+        <v>323717</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1219</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>778209</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>422</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>383929</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>168924</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>850</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>877188</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1525107</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106</v>
+      </c>
+      <c r="C10" t="n">
+        <v>138616</v>
+      </c>
+      <c r="D10" t="n">
+        <v>51205</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>119191</v>
+      </c>
+      <c r="G10" t="n">
+        <v>295</v>
+      </c>
+      <c r="H10" t="n">
+        <v>367286</v>
+      </c>
+      <c r="I10" t="n">
+        <v>415092</v>
+      </c>
+      <c r="J10" t="n">
+        <v>131794</v>
+      </c>
+      <c r="K10" t="n">
+        <v>296</v>
+      </c>
+      <c r="L10" t="n">
+        <v>340606</v>
+      </c>
+      <c r="M10" t="n">
+        <v>142242</v>
+      </c>
+      <c r="N10" t="n">
+        <v>245</v>
+      </c>
+      <c r="O10" t="n">
+        <v>286640</v>
+      </c>
+      <c r="P10" t="n">
+        <v>263834</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1986</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>347</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>289885</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>86788</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>751</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>797773</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>553085</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93</v>
+      </c>
+      <c r="C11" t="n">
+        <v>108026</v>
+      </c>
+      <c r="D11" t="n">
+        <v>91198</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>95748</v>
+      </c>
+      <c r="G11" t="n">
+        <v>329</v>
+      </c>
+      <c r="H11" t="n">
+        <v>389610</v>
+      </c>
+      <c r="I11" t="n">
+        <v>482786</v>
+      </c>
+      <c r="J11" t="n">
+        <v>138130.58</v>
+      </c>
+      <c r="K11" t="n">
+        <v>157</v>
+      </c>
+      <c r="L11" t="n">
+        <v>180434</v>
+      </c>
+      <c r="M11" t="n">
+        <v>143004</v>
+      </c>
+      <c r="N11" t="n">
+        <v>244</v>
+      </c>
+      <c r="O11" t="n">
+        <v>277603</v>
+      </c>
+      <c r="P11" t="n">
+        <v>329236</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1317</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>313</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>259659</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>87491</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>735</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>757295</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>662792</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B12" t="n">
+        <v>77</v>
+      </c>
+      <c r="C12" t="n">
+        <v>96054</v>
+      </c>
+      <c r="D12" t="n">
+        <v>62903</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>77493</v>
+      </c>
+      <c r="G12" t="n">
+        <v>338</v>
+      </c>
+      <c r="H12" t="n">
+        <v>405417</v>
+      </c>
+      <c r="I12" t="n">
+        <v>472575</v>
+      </c>
+      <c r="J12" t="n">
+        <v>126605.85</v>
+      </c>
+      <c r="K12" t="n">
+        <v>294</v>
+      </c>
+      <c r="L12" t="n">
+        <v>320989</v>
+      </c>
+      <c r="M12" t="n">
+        <v>165125</v>
+      </c>
+      <c r="N12" t="n">
+        <v>229</v>
+      </c>
+      <c r="O12" t="n">
+        <v>257874</v>
+      </c>
+      <c r="P12" t="n">
+        <v>287107</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1701</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>243</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>213247</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>110027</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>658</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>714718</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>647206</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83</v>
+      </c>
+      <c r="C13" t="n">
+        <v>111959</v>
+      </c>
+      <c r="D13" t="n">
+        <v>59986</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>106955</v>
+      </c>
+      <c r="G13" t="n">
+        <v>515</v>
+      </c>
+      <c r="H13" t="n">
+        <v>601531</v>
+      </c>
+      <c r="I13" t="n">
+        <v>421187</v>
+      </c>
+      <c r="J13" t="n">
+        <v>146738</v>
+      </c>
+      <c r="K13" t="n">
+        <v>236</v>
+      </c>
+      <c r="L13" t="n">
+        <v>282533</v>
+      </c>
+      <c r="M13" t="n">
+        <v>172993</v>
+      </c>
+      <c r="N13" t="n">
+        <v>279</v>
+      </c>
+      <c r="O13" t="n">
+        <v>315998</v>
+      </c>
+      <c r="P13" t="n">
+        <v>295520</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>585</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>556</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>461033</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>104409</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1155</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1175108</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>585582</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B14" t="n">
+        <v>89</v>
+      </c>
+      <c r="C14" t="n">
+        <v>109047</v>
+      </c>
+      <c r="D14" t="n">
+        <v>62687</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>104193</v>
+      </c>
+      <c r="G14" t="n">
+        <v>415</v>
+      </c>
+      <c r="H14" t="n">
+        <v>472849</v>
+      </c>
+      <c r="I14" t="n">
+        <v>455364</v>
+      </c>
+      <c r="J14" t="n">
+        <v>110359</v>
+      </c>
+      <c r="K14" t="n">
+        <v>147</v>
+      </c>
+      <c r="L14" t="n">
+        <v>181952</v>
+      </c>
+      <c r="M14" t="n">
+        <v>136625</v>
+      </c>
+      <c r="N14" t="n">
+        <v>268</v>
+      </c>
+      <c r="O14" t="n">
+        <v>290897</v>
+      </c>
+      <c r="P14" t="n">
+        <v>299984</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2269</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1275288</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>470</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>390853</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>151404</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3248</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2252037</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>669455</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98</v>
+      </c>
+      <c r="C15" t="n">
+        <v>137076</v>
+      </c>
+      <c r="D15" t="n">
+        <v>47998</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>129174</v>
+      </c>
+      <c r="G15" t="n">
+        <v>290</v>
+      </c>
+      <c r="H15" t="n">
+        <v>333657</v>
+      </c>
+      <c r="I15" t="n">
+        <v>446808</v>
+      </c>
+      <c r="J15" t="n">
+        <v>75122</v>
+      </c>
+      <c r="K15" t="n">
+        <v>140</v>
+      </c>
+      <c r="L15" t="n">
+        <v>168950</v>
+      </c>
+      <c r="M15" t="n">
+        <v>135260</v>
+      </c>
+      <c r="N15" t="n">
+        <v>210</v>
+      </c>
+      <c r="O15" t="n">
+        <v>235857</v>
+      </c>
+      <c r="P15" t="n">
+        <v>309024</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>680</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>199</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>169440</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>194876</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>587</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>640173</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>690362</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79</v>
+      </c>
+      <c r="C16" t="n">
+        <v>118795</v>
+      </c>
+      <c r="D16" t="n">
+        <v>55177</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>72662</v>
+      </c>
+      <c r="G16" t="n">
+        <v>291</v>
+      </c>
+      <c r="H16" t="n">
+        <v>337291</v>
+      </c>
+      <c r="I16" t="n">
+        <v>534224</v>
+      </c>
+      <c r="J16" t="n">
+        <v>96462</v>
+      </c>
+      <c r="K16" t="n">
+        <v>155</v>
+      </c>
+      <c r="L16" t="n">
+        <v>190758</v>
+      </c>
+      <c r="M16" t="n">
+        <v>186516</v>
+      </c>
+      <c r="N16" t="n">
+        <v>216</v>
+      </c>
+      <c r="O16" t="n">
+        <v>235075</v>
+      </c>
+      <c r="P16" t="n">
+        <v>349541</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1560</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2789</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>613268</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>212</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>189358</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>180051</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>583</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>647004</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1385509</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80</v>
+      </c>
+      <c r="C17" t="n">
+        <v>101507</v>
+      </c>
+      <c r="D17" t="n">
+        <v>80340</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>95372</v>
+      </c>
+      <c r="G17" t="n">
+        <v>271</v>
+      </c>
+      <c r="H17" t="n">
+        <v>321147</v>
+      </c>
+      <c r="I17" t="n">
+        <v>423259</v>
+      </c>
+      <c r="J17" t="n">
+        <v>71541.95</v>
+      </c>
+      <c r="K17" t="n">
+        <v>138</v>
+      </c>
+      <c r="L17" t="n">
+        <v>172090</v>
+      </c>
+      <c r="M17" t="n">
+        <v>159713</v>
+      </c>
+      <c r="N17" t="n">
+        <v>220</v>
+      </c>
+      <c r="O17" t="n">
+        <v>234439</v>
+      </c>
+      <c r="P17" t="n">
+        <v>252176</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2290</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>185</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>191616</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>104598</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>536</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>614270</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>610487</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B18" t="n">
+        <v>61</v>
+      </c>
+      <c r="C18" t="n">
+        <v>78711</v>
+      </c>
+      <c r="D18" t="n">
+        <v>129196</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>54470</v>
+      </c>
+      <c r="G18" t="n">
+        <v>334</v>
+      </c>
+      <c r="H18" t="n">
+        <v>398349</v>
+      </c>
+      <c r="I18" t="n">
+        <v>429308</v>
+      </c>
+      <c r="J18" t="n">
+        <v>75000.03999999999</v>
+      </c>
+      <c r="K18" t="n">
+        <v>80</v>
+      </c>
+      <c r="L18" t="n">
+        <v>113356</v>
+      </c>
+      <c r="M18" t="n">
+        <v>128819</v>
+      </c>
+      <c r="N18" t="n">
+        <v>254</v>
+      </c>
+      <c r="O18" t="n">
+        <v>284993</v>
+      </c>
+      <c r="P18" t="n">
+        <v>308649</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2861</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>197</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>163403</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>125511</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>592</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>640463</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>686876</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B19" t="n">
+        <v>64</v>
+      </c>
+      <c r="C19" t="n">
+        <v>69627</v>
+      </c>
+      <c r="D19" t="n">
+        <v>102617</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>65972</v>
+      </c>
+      <c r="G19" t="n">
+        <v>333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>392774</v>
+      </c>
+      <c r="I19" t="n">
+        <v>537858</v>
+      </c>
+      <c r="J19" t="n">
+        <v>132687</v>
+      </c>
+      <c r="K19" t="n">
+        <v>91</v>
+      </c>
+      <c r="L19" t="n">
+        <v>126372</v>
+      </c>
+      <c r="M19" t="n">
+        <v>191576</v>
+      </c>
+      <c r="N19" t="n">
+        <v>242</v>
+      </c>
+      <c r="O19" t="n">
+        <v>266402</v>
+      </c>
+      <c r="P19" t="n">
+        <v>348862</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1640</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>166</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>142420</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>139950</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>563</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>604821</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>782065</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B20" t="n">
+        <v>35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>48665</v>
+      </c>
+      <c r="D20" t="n">
+        <v>107604</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>46762</v>
+      </c>
+      <c r="G20" t="n">
+        <v>380</v>
+      </c>
+      <c r="H20" t="n">
+        <v>450065</v>
+      </c>
+      <c r="I20" t="n">
+        <v>536567</v>
+      </c>
+      <c r="J20" t="n">
+        <v>126818.18</v>
+      </c>
+      <c r="K20" t="n">
+        <v>102</v>
+      </c>
+      <c r="L20" t="n">
+        <v>136392</v>
+      </c>
+      <c r="M20" t="n">
+        <v>209260</v>
+      </c>
+      <c r="N20" t="n">
+        <v>278</v>
+      </c>
+      <c r="O20" t="n">
+        <v>313673</v>
+      </c>
+      <c r="P20" t="n">
+        <v>331962</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1611</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>391</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>344341</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>100984</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>807</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>844682</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>745155</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B21" t="n">
+        <v>68</v>
+      </c>
+      <c r="C21" t="n">
+        <v>77794</v>
+      </c>
+      <c r="D21" t="n">
+        <v>49794</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>73921</v>
+      </c>
+      <c r="G21" t="n">
+        <v>467</v>
+      </c>
+      <c r="H21" t="n">
+        <v>540776</v>
+      </c>
+      <c r="I21" t="n">
+        <v>431154</v>
+      </c>
+      <c r="J21" t="n">
+        <v>144160.25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>133</v>
+      </c>
+      <c r="L21" t="n">
+        <v>162475</v>
+      </c>
+      <c r="M21" t="n">
+        <v>172468</v>
+      </c>
+      <c r="N21" t="n">
+        <v>334</v>
+      </c>
+      <c r="O21" t="n">
+        <v>378301</v>
+      </c>
+      <c r="P21" t="n">
+        <v>263816</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1457</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4539</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1462</v>
+      </c>
+      <c r="X21" t="n">
+        <v>970942</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>389</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>328924</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>122410</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2388</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1919893</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>607897</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B22" t="n">
+        <v>68</v>
+      </c>
+      <c r="C22" t="n">
+        <v>118249</v>
+      </c>
+      <c r="D22" t="n">
+        <v>69240</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>108897</v>
+      </c>
+      <c r="G22" t="n">
+        <v>360</v>
+      </c>
+      <c r="H22" t="n">
+        <v>485773</v>
+      </c>
+      <c r="I22" t="n">
+        <v>462080</v>
+      </c>
+      <c r="J22" t="n">
+        <v>126866.73</v>
+      </c>
+      <c r="K22" t="n">
+        <v>180</v>
+      </c>
+      <c r="L22" t="n">
+        <v>241684</v>
+      </c>
+      <c r="M22" t="n">
+        <v>185709</v>
+      </c>
+      <c r="N22" t="n">
+        <v>205</v>
+      </c>
+      <c r="O22" t="n">
+        <v>245499</v>
+      </c>
+      <c r="P22" t="n">
+        <v>282791</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>851</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>172</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>130392</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>191253</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>601</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>735265</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>722573</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B23" t="n">
+        <v>66</v>
+      </c>
+      <c r="C23" t="n">
+        <v>100508</v>
+      </c>
+      <c r="D23" t="n">
+        <v>57008</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>71561</v>
+      </c>
+      <c r="G23" t="n">
+        <v>389</v>
+      </c>
+      <c r="H23" t="n">
+        <v>472792</v>
+      </c>
+      <c r="I23" t="n">
+        <v>483531</v>
+      </c>
+      <c r="J23" t="n">
+        <v>125305.89</v>
+      </c>
+      <c r="K23" t="n">
+        <v>227</v>
+      </c>
+      <c r="L23" t="n">
+        <v>301973</v>
+      </c>
+      <c r="M23" t="n">
+        <v>156406</v>
+      </c>
+      <c r="N23" t="n">
+        <v>248</v>
+      </c>
+      <c r="O23" t="n">
+        <v>280214</v>
+      </c>
+      <c r="P23" t="n">
+        <v>333204</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>607</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>609352</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>137</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>112685</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>174970</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>593</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>686592</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1324861</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B24" t="n">
+        <v>54</v>
+      </c>
+      <c r="C24" t="n">
+        <v>63449</v>
+      </c>
+      <c r="D24" t="n">
+        <v>79811</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>58298</v>
+      </c>
+      <c r="G24" t="n">
+        <v>396</v>
+      </c>
+      <c r="H24" t="n">
+        <v>449824</v>
+      </c>
+      <c r="I24" t="n">
+        <v>426383</v>
+      </c>
+      <c r="J24" t="n">
+        <v>75734.33</v>
+      </c>
+      <c r="K24" t="n">
+        <v>179</v>
+      </c>
+      <c r="L24" t="n">
+        <v>211755</v>
+      </c>
+      <c r="M24" t="n">
+        <v>148967</v>
+      </c>
+      <c r="N24" t="n">
+        <v>263</v>
+      </c>
+      <c r="O24" t="n">
+        <v>290691</v>
+      </c>
+      <c r="P24" t="n">
+        <v>276298</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2313</v>
+      </c>
+      <c r="V24" t="n">
+        <v>853</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>151</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>131461</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>141505</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>603</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>647047</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>752310</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B25" t="n">
+        <v>62</v>
+      </c>
+      <c r="C25" t="n">
+        <v>100526</v>
+      </c>
+      <c r="D25" t="n">
+        <v>68547</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>86807</v>
+      </c>
+      <c r="G25" t="n">
+        <v>435</v>
+      </c>
+      <c r="H25" t="n">
+        <v>501457</v>
+      </c>
+      <c r="I25" t="n">
+        <v>506643.76</v>
+      </c>
+      <c r="J25" t="n">
+        <v>108754.3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>179</v>
+      </c>
+      <c r="L25" t="n">
+        <v>230832</v>
+      </c>
+      <c r="M25" t="n">
+        <v>172007</v>
+      </c>
+      <c r="N25" t="n">
+        <v>286</v>
+      </c>
+      <c r="O25" t="n">
+        <v>293352</v>
+      </c>
+      <c r="P25" t="n">
+        <v>323498</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2316</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5029</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>202</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>190620</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>123916</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>701</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>794919</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>807893.76</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B26" t="n">
+        <v>64</v>
+      </c>
+      <c r="C26" t="n">
+        <v>89889</v>
+      </c>
+      <c r="D26" t="n">
+        <v>75711</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>52678</v>
+      </c>
+      <c r="G26" t="n">
+        <v>357</v>
+      </c>
+      <c r="H26" t="n">
+        <v>404215</v>
+      </c>
+      <c r="I26" t="n">
+        <v>506555</v>
+      </c>
+      <c r="J26" t="n">
+        <v>32875.25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>132</v>
+      </c>
+      <c r="L26" t="n">
+        <v>167691</v>
+      </c>
+      <c r="M26" t="n">
+        <v>171436</v>
+      </c>
+      <c r="N26" t="n">
+        <v>247</v>
+      </c>
+      <c r="O26" t="n">
+        <v>273597</v>
+      </c>
+      <c r="P26" t="n">
+        <v>331583</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2508</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1007</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>186</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>174329</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>119763</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>609</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>670941</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>806794</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B27" t="n">
+        <v>54</v>
+      </c>
+      <c r="C27" t="n">
+        <v>59046</v>
+      </c>
+      <c r="D27" t="n">
+        <v>61126</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>56616</v>
+      </c>
+      <c r="G27" t="n">
+        <v>466</v>
+      </c>
+      <c r="H27" t="n">
+        <v>543034</v>
+      </c>
+      <c r="I27" t="n">
+        <v>491482</v>
+      </c>
+      <c r="J27" t="n">
+        <v>70850.44</v>
+      </c>
+      <c r="K27" t="n">
+        <v>133</v>
+      </c>
+      <c r="L27" t="n">
+        <v>176129</v>
+      </c>
+      <c r="M27" t="n">
+        <v>129972</v>
+      </c>
+      <c r="N27" t="n">
+        <v>339</v>
+      </c>
+      <c r="O27" t="n">
+        <v>369336</v>
+      </c>
+      <c r="P27" t="n">
+        <v>354744</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4425</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1544</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>350</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>333052</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>241915</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>874</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>939557</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>899825</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B28" t="n">
+        <v>88</v>
+      </c>
+      <c r="C28" t="n">
+        <v>133334</v>
+      </c>
+      <c r="D28" t="n">
+        <v>70556</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>127998</v>
+      </c>
+      <c r="G28" t="n">
+        <v>533</v>
+      </c>
+      <c r="H28" t="n">
+        <v>613669</v>
+      </c>
+      <c r="I28" t="n">
+        <v>433966</v>
+      </c>
+      <c r="J28" t="n">
+        <v>121805.71</v>
+      </c>
+      <c r="K28" t="n">
+        <v>130</v>
+      </c>
+      <c r="L28" t="n">
+        <v>166479</v>
+      </c>
+      <c r="M28" t="n">
+        <v>123303</v>
+      </c>
+      <c r="N28" t="n">
+        <v>398</v>
+      </c>
+      <c r="O28" t="n">
+        <v>438337</v>
+      </c>
+      <c r="P28" t="n">
+        <v>283140</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>3314</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>312</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>291210</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>194522</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>933</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1038213</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>806116</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B29" t="n">
+        <v>53</v>
+      </c>
+      <c r="C29" t="n">
+        <v>73912</v>
+      </c>
+      <c r="D29" t="n">
+        <v>153078</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>70837</v>
+      </c>
+      <c r="G29" t="n">
+        <v>397</v>
+      </c>
+      <c r="H29" t="n">
+        <v>453996</v>
+      </c>
+      <c r="I29" t="n">
+        <v>434403</v>
+      </c>
+      <c r="J29" t="n">
+        <v>38029</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1441</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1858</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1864</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1313698</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>103758</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>193</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>172579</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>297136</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2509</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2015626</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>990233</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B30" t="n">
+        <v>66</v>
+      </c>
+      <c r="C30" t="n">
+        <v>85641</v>
+      </c>
+      <c r="D30" t="n">
+        <v>60533</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>59797</v>
+      </c>
+      <c r="G30" t="n">
+        <v>395</v>
+      </c>
+      <c r="H30" t="n">
+        <v>431351</v>
+      </c>
+      <c r="I30" t="n">
+        <v>517181</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>594</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2052</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>462</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>517586</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>579766</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B31" t="n">
+        <v>63</v>
+      </c>
+      <c r="C31" t="n">
+        <v>106264</v>
+      </c>
+      <c r="D31" t="n">
+        <v>89783</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" t="n">
+        <v>101469</v>
+      </c>
+      <c r="G31" t="n">
+        <v>413</v>
+      </c>
+      <c r="H31" t="n">
+        <v>458901</v>
+      </c>
+      <c r="I31" t="n">
+        <v>458013</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1036</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>476</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>565165</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>548832</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B32" t="n">
+        <v>54</v>
+      </c>
+      <c r="C32" t="n">
+        <v>93127</v>
+      </c>
+      <c r="D32" t="n">
+        <v>89783</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>86522</v>
+      </c>
+      <c r="G32" t="n">
+        <v>402</v>
+      </c>
+      <c r="H32" t="n">
+        <v>460790</v>
+      </c>
+      <c r="I32" t="n">
+        <v>469773</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1609</v>
+      </c>
+      <c r="V32" t="n">
+        <v>594</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>457</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>555526</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>560150</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B33" t="n">
+        <v>73</v>
+      </c>
+      <c r="C33" t="n">
+        <v>110359</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>86153</v>
+      </c>
+      <c r="G33" t="n">
+        <v>478</v>
+      </c>
+      <c r="H33" t="n">
+        <v>558642</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>53296</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2129</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="n">
+        <v>554</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>671130</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -3187,31 +4914,31 @@
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>2225</v>
+        <v>2298</v>
       </c>
       <c r="C35" t="n">
-        <v>3009325</v>
+        <v>3119684</v>
       </c>
       <c r="D35" t="n">
         <v>2248252</v>
       </c>
       <c r="E35" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F35" t="n">
-        <v>2608798</v>
+        <v>2694951</v>
       </c>
       <c r="G35" t="n">
-        <v>14216</v>
+        <v>15096</v>
       </c>
       <c r="H35" t="n">
-        <v>16356799</v>
+        <v>17376231</v>
       </c>
       <c r="I35" t="n">
-        <v>13587590.76</v>
+        <v>14057363.76</v>
       </c>
       <c r="J35" t="n">
-        <v>3470460.19</v>
+        <v>3523756.19</v>
       </c>
       <c r="K35" t="n">
         <v>4919</v>
@@ -3241,10 +4968,10 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="U35" t="n">
-        <v>40925</v>
+        <v>43054</v>
       </c>
       <c r="V35" t="n">
         <v>50038</v>
@@ -3268,27 +4995,27 @@
         <v>4030860</v>
       </c>
       <c r="AC35" t="n">
-        <v>31633</v>
+        <v>32589</v>
       </c>
       <c r="AD35" t="n">
-        <v>30850999</v>
+        <v>31982919</v>
       </c>
       <c r="AE35" t="n">
-        <v>22540117.76</v>
+        <v>23009890.76</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.338517657273295</v>
+        <v>0.387604236535762</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0.2038042128963855</v>
+        <v>0.2360945691285149</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -3320,21 +5047,21 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="n">
-        <v>0.3687150763137804</v>
+        <v>0.3899639652178861</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>3588041.346153846</v>
+        <v>3719623.230769231</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>17484854.10344828</v>
+        <v>17376231</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -3353,7 +5080,7 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
-        <v>50747</v>
+        <v>53386.96</v>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
@@ -3368,7 +5095,7 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="n">
-        <v>45292593.24589842</v>
+        <v>45318191.98706552</v>
       </c>
     </row>
     <row r="39">
@@ -3377,7 +5104,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>400527</v>
+        <v>424733</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -3438,7 +5165,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="n">
-        <v>103449127.3958984</v>
+        <v>103474726.1370655</v>
       </c>
     </row>
     <row r="41">
@@ -3467,7 +5194,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6739,7 +8466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9946,7 +11673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12918,7 +14645,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15617,7 +17344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18033,7 +19760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20323,7 +22050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
